--- a/docs/StructureDefinition-LTCCareTeam.xlsx
+++ b/docs/StructureDefinition-LTCCareTeam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCareTeam.xlsx
+++ b/docs/StructureDefinition-LTCCareTeam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCareTeam.xlsx
+++ b/docs/StructureDefinition-LTCCareTeam.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCareTeam.xlsx
+++ b/docs/StructureDefinition-LTCCareTeam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCareTeam.xlsx
+++ b/docs/StructureDefinition-LTCCareTeam.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1507" uniqueCount="296">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -256,10 +256,10 @@
 </t>
   </si>
   <si>
-    <t>Planned participants in the coordination and delivery of care for a patient or group</t>
-  </si>
-  <si>
-    <t>The Care Team includes all the people and organizations who plan to participate in the coordination and delivery of care for a patient.</t>
+    <t>在健康照護過程中提供服務的照護團隊</t>
+  </si>
+  <si>
+    <t>指明受照護者所需要的團隊，此資源用來識別參與關照受照護者或為受照護者(個人或群體)提供醫療保健服務的一群人及其在團隊中的角色。</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -282,13 +282,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>不重複的 ID 用以識別儲存在特定 FHIR Server 中的 CareTeam 紀錄，通常又稱為邏輯性 ID。</t>
+  </si>
+  <si>
+    <t>resource 的邏輯 ID，在 resource 的 URL 中使用。一旦指定，這個值永遠不會改變。</t>
+  </si>
+  <si>
+    <t>一個 resource 使用新增操作(create operation)提交給伺服器時，此 resource 沒有 id，它的 id 在 resource 被創建後由伺器分配/指定。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -301,10 +301,10 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>此 CareTeam Resource 的 metadata</t>
+  </si>
+  <si>
+    <t>關於 resource 的 metadata。這是由基礎建設維護的內容。內容的更改可能並不總是與 resource 的版本更改相關聯。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -340,19 +340,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>用以表述 CareTeam Resource 內容的語言。</t>
+  </si>
+  <si>
+    <t>編寫此 resource 的語言</t>
+  </si>
+  <si>
+    <t>提供語言是為了支援索引和可存取性(通常，文字表述轉語音等服務使用此語言標籤)。html lanuage tag 適用於此敘述。resource 上的語言標籤可用於指定從 resource 中的資料所產成的其他表述之語言。不是所有的內容都必須使用此語言。不應該假定 Resource.language 自動適用於敘述。如果指定語言，它也應該被指定在 html 中的 div 資料項目(關於 xml:lang 和 html lang 屬性之間的關係，見 HTML5 中的規則)。</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>A human language.</t>
+    <t>人類語言；鼓勵使用 CommonLanguages 代碼表中的代碼，但不強制一定要使用此代碼表，你也可使用其他代碼表的代碼或單純以文字表示。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -484,7 +484,7 @@
     <t>照顧團隊的狀態。[應填入 proposed / active / suspended / inactive / entered-in-error]</t>
   </si>
   <si>
-    <t>Indicates the current state of the care team.</t>
+    <t>照護團隊目前的狀態。</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains the code entered-in-error that marks the care team as not currently valid.</t>
@@ -524,7 +524,7 @@
     <t>Indicates the type of care team.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/care-team-category</t>
+    <t>http://hl7.org/fhir/ValueSet/care-team-category|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.class</t>
@@ -560,7 +560,10 @@
     <t>照顧團隊的適用主體，即這個照顧團隊的適用對象是誰？</t>
   </si>
   <si>
-    <t>Identifies the patient or group whose intended care is handled by the team.</t>
+    <t>照護團隊所關照的個人或群體。</t>
+  </si>
+  <si>
+    <t>參照可能是相對的，絕對的或內部的。</t>
   </si>
   <si>
     <t>Allows the team to care for a group (e.g. marriage) therapy. 
@@ -691,13 +694,13 @@
 </t>
   </si>
   <si>
-    <t>Encounter created as part of</t>
-  </si>
-  <si>
-    <t>The Encounter during which this CareTeam was created or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
+    <t>與此 CareTeam 相關的就醫事件</t>
+  </si>
+  <si>
+    <t>此 CareTeam 是在哪次就醫情境中確定或修正的。</t>
+  </si>
+  <si>
+    <t>此資料項目不用於記錄照護團隊負責的所有就診。就診用來提供建立或變更照護團隊的情境。</t>
   </si>
   <si>
     <t>FiveWs.context</t>
@@ -732,7 +735,7 @@
     <t>照顧團隊的參與者，即這個照顧團隊是由哪些人參與的？</t>
   </si>
   <si>
-    <t>Identifies all people and organizations who are expected to be involved in the care team.</t>
+    <t>照護團隊的成員，包含他們在團隊中扮演的角色和負責的時間段。</t>
   </si>
   <si>
     <t xml:space="preserve">ctm-1
@@ -778,7 +781,7 @@
     <t>照顧團隊參與者的角色</t>
   </si>
   <si>
-    <t>Indicates specific responsibility of an individual within the care team, such as "Primary care physician", "Trained social worker counselor", "Caregiver", etc.</t>
+    <t>指明此照護團隊成員在團隊中所扮演的角色。</t>
   </si>
   <si>
     <t>Roles may sometimes be inferred by type of Practitioner.  These are relationships that hold only within the context of the care team.  General relationships should be handled as properties of the Patient resource directly.</t>
@@ -803,11 +806,7 @@
     <t>照顧團隊的成員</t>
   </si>
   <si>
-    <t>The specific person or organization who is participating/expected to participate in the care team.</t>
-  </si>
-  <si>
-    <t>Patient only needs to be listed if they have a role other than "subject of care".
-Member is optional because some participants may be known only by their role, particularly in draft plans.</t>
+    <t>團隊成員可能是個人、組織、照護者，或是具有特定角色的醫事人員，或是將角色代表給特定個人或組織的醫事職務。</t>
   </si>
   <si>
     <t>FiveWs.actor</t>
@@ -847,10 +846,13 @@
 </t>
   </si>
   <si>
-    <t>Organization of the practitioner</t>
-  </si>
-  <si>
-    <t>The organization of the practitioner.</t>
+    <t>組織成員代表誰</t>
+  </si>
+  <si>
+    <t>團隊成員代表的組織。</t>
+  </si>
+  <si>
+    <t>若成員是個人，此資料項目可用來表示此個人代表某個組織。</t>
   </si>
   <si>
     <t>Practitioners can be associated with multiple organizations.  This element indicates which organization they were acting on behalf of.</t>
@@ -877,7 +879,7 @@
     <t>Indicates the reason for the care team.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>FiveWs.why[x]</t>
@@ -890,16 +892,25 @@
 </t>
   </si>
   <si>
-    <t>Condition(s) that this care team addresses.</t>
+    <t>為何需要此照護團隊</t>
+  </si>
+  <si>
+    <t>描述建立照護團隊的原因或需要照護團隊服務的情況。</t>
+  </si>
+  <si>
+    <t>可能的原因包括：病人目前的健康狀況、潛在的健康問題、複雜的醫療需求、已安排的程序(例如：手術)或出院後服務計畫。</t>
   </si>
   <si>
     <t>CareTeam.managingOrganization</t>
   </si>
   <si>
-    <t>Organization responsible for the care team</t>
-  </si>
-  <si>
-    <t>The organization responsible for the care team.</t>
+    <t>照護團隊所屬的組織</t>
+  </si>
+  <si>
+    <t>負責召集或管理此照護團隊的組織。</t>
+  </si>
+  <si>
+    <t>此資料項目與 participant.member 中包含的組織不同，它特指負責管理照護團隊的組織。</t>
   </si>
   <si>
     <t>Allows for multiple organizations to collaboratively manage cross-organizational, longitudinal care plan.</t>
@@ -1275,8 +1286,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="51.97265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="38.78125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="100.8515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="42.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -2889,9 +2900,11 @@
       <c r="M15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="N15" s="2"/>
+      <c r="N15" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -2955,7 +2968,7 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
@@ -2966,10 +2979,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2995,10 +3008,10 @@
         <v>166</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3049,7 +3062,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3070,15 +3083,15 @@
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3107,7 +3120,7 @@
         <v>131</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>133</v>
@@ -3148,19 +3161,19 @@
         <v>20</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3181,15 +3194,15 @@
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3215,13 +3228,13 @@
         <v>166</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3271,7 +3284,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3280,7 +3293,7 @@
         <v>84</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>96</v>
@@ -3297,10 +3310,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3326,13 +3339,13 @@
         <v>98</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3358,13 +3371,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3382,7 +3395,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3408,10 +3421,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3437,13 +3450,13 @@
         <v>142</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3493,7 +3506,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3514,15 +3527,15 @@
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3548,13 +3561,13 @@
         <v>166</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3604,7 +3617,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3630,10 +3643,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3656,16 +3669,16 @@
         <v>85</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3715,7 +3728,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3730,7 +3743,7 @@
         <v>96</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
@@ -3741,10 +3754,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3767,17 +3780,17 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -3826,7 +3839,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3841,7 +3854,7 @@
         <v>96</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
@@ -3852,10 +3865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3878,13 +3891,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3935,7 +3948,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3944,27 +3957,27 @@
         <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3990,10 +4003,10 @@
         <v>166</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4044,7 +4057,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4065,15 +4078,15 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4102,7 +4115,7 @@
         <v>131</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N26" t="s" s="2">
         <v>133</v>
@@ -4155,7 +4168,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4176,19 +4189,19 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4210,10 +4223,10 @@
         <v>130</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>133</v>
@@ -4268,7 +4281,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4294,10 +4307,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4323,13 +4336,13 @@
         <v>156</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4359,7 +4372,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -4377,7 +4390,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4395,18 +4408,18 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4429,16 +4442,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>251</v>
+        <v>175</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4488,7 +4501,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4543,10 +4556,10 @@
         <v>166</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4597,7 +4610,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4618,7 +4631,7 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -4655,7 +4668,7 @@
         <v>131</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>133</v>
@@ -4696,19 +4709,19 @@
         <v>20</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4729,7 +4742,7 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32">
@@ -4766,10 +4779,10 @@
         <v>258</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4819,7 +4832,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -4828,7 +4841,7 @@
         <v>84</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>96</v>
@@ -4874,13 +4887,13 @@
         <v>98</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -4906,13 +4919,13 @@
         <v>20</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -4930,7 +4943,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -4985,13 +4998,13 @@
         <v>142</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5041,7 +5054,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5062,7 +5075,7 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -5096,13 +5109,13 @@
         <v>166</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5152,7 +5165,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5212,9 +5225,11 @@
       <c r="M36" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="N36" s="2"/>
+      <c r="N36" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="O36" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5289,10 +5304,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5315,13 +5330,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5372,7 +5387,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5398,10 +5413,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5427,10 +5442,10 @@
         <v>156</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5460,10 +5475,10 @@
         <v>161</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -5481,7 +5496,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5496,7 +5511,7 @@
         <v>96</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -5507,10 +5522,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5533,15 +5548,17 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -5590,7 +5607,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5605,7 +5622,7 @@
         <v>96</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>20</v>
@@ -5616,10 +5633,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5645,14 +5662,16 @@
         <v>263</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>284</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>285</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -5701,7 +5720,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5727,10 +5746,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5753,16 +5772,16 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5812,7 +5831,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -5838,10 +5857,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5864,13 +5883,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5921,7 +5940,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>

--- a/docs/StructureDefinition-LTCCareTeam.xlsx
+++ b/docs/StructureDefinition-LTCCareTeam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCCareTeam.xlsx
+++ b/docs/StructureDefinition-LTCCareTeam.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
